--- a/05_Figures/F05_classification/proteins/trajectory/HR_LR/pam/c_data/results.xlsx
+++ b/05_Figures/F05_classification/proteins/trajectory/HR_LR/pam/c_data/results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="528">
   <si>
     <t xml:space="preserve">level</t>
   </si>
@@ -131,1032 +131,1356 @@
     <t xml:space="preserve">freq</t>
   </si>
   <si>
+    <t xml:space="preserve">ACAA1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACAT1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACO2@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACSF2@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACSF2@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACSF2@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACSL1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACSS2@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACSS2@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACTR1A@T3</t>
+  </si>
+  <si>
     <t xml:space="preserve">ACY1@T3</t>
   </si>
   <si>
+    <t xml:space="preserve">AFG3L2@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AHCYL2@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIFM1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIMP1@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIMP2@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AK1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AK2@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AKT2@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALDH1A1@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALDH1A1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALDH1L1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALDH3A2@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALDOA@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALDOC@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALPK3@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALPK3@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMPD1@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMPD1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMPD3@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANXA11@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANXA2@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANXA5@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANXA5@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANXA7@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AP2M1@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APEH@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APOO@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AQP1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARHGAP19@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARL6IP5@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARL8A@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARMT1@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARMT1@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARPP19@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATAD3A@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATG3@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATIC@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP2A3@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP5F1E@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP5MD@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP5MF@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP5PB@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP5PD@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP6V1H@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BCL2L13@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BDH1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BDH2@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BDH2@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLMH@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLVRA@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLVRA@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOLA2@T3</t>
+  </si>
+  <si>
     <t xml:space="preserve">BPNT1@T3</t>
   </si>
   <si>
+    <t xml:space="preserve">BSG@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BZW1@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C11orf54@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C11orf68@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA3@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CACNB3@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CALR@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMK2A@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMK2D@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMK2G@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANX@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANX@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPN2@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CASQ1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAVIN4@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD59@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHCHD2@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHCHD7@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHMP2A@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIRBP@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIRBP@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CISD2@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CKM@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLIP1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLPP@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLYBL@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLYBL@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMPK1@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CNDP2@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CNIH4@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COL18A1@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COL4A2@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMT@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMT@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COQ3@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COQ8A@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COX19@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COX5A@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COX6B1@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COX7A1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CPNE1@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CPT1A@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CPT1A@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CPT1B@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CPT2@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRIP2@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSDE1@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CTBP1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CTPS1@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUL1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUL2@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CYB5R1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CYCS@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCTN4@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCUN1D1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DDX1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DHRS7@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DLAT@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DLST@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DLST@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMD@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DNAJA3@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DNAJA3@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DNAJA4@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DUSP3@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DYNC1H1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DYNC1I2@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DYNLT1@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECHDC2@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECHDC2@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECPAS@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EEF1A1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EEF1A2@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EEF1D@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EEF2@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF2A@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF2A@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF2S3@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF3B@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF3C@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF3C@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF3E@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF3F@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF3G@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF3G@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF3G@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF3L@T1</t>
+  </si>
+  <si>
     <t xml:space="preserve">EIF4A2@T3</t>
   </si>
   <si>
+    <t xml:space="preserve">EIF4H@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF5A@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELOB@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELOC@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENDOD1@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENO2@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENO3@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EPB41L2@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EPM2A@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERI3@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERO1A@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESYT2@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EZR@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FABP3@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAH@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAM114A2@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAM98B@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FARSB@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FARSB@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FECH@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FHL1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FITM1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FITM2@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FITM2@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FKBP4@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLOT2@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FTH1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FXYD1@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAA@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GANAB@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAPDH@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAPDHS@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GARNL3@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GATD3B@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLOD4@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLRX3@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLRX5@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLUL@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GMPPB@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GOT2@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPI@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPX1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPX4@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRSF1@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSTP1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GYPC@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HADHA@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HARS1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HBS1L@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HCCS@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HDHD2@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HDHD2@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HECTD1@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HINT1@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HINT3@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HLA-A@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HMGCL@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HMGCL@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HNRNPDL@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HNRNPK@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HNRNPK@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPCAL1@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSPB1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSPB2@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSPB3@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSPB3@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IFITM1@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IPO7@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISCU@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISYNA1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JPT2@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KCTD12@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIF5B@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAMTOR1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAMTOR3@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LANCL1@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LANCL2@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAP3@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LDHD@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LETM1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LMAN2@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LMOD3@T3</t>
+  </si>
+  <si>
     <t xml:space="preserve">LNPK@T3</t>
   </si>
   <si>
+    <t xml:space="preserve">LONP1@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LPCAT3@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LPCAT3@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LYPLA2@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LYRM7@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LZIC@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAN2C1@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAP1LC3B2@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAP1LC3B2@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAP2K1@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAP2K1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAP2K2@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAP2K2@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAP2K2@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAP3K20@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAPRE2@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAPRE3@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MBNL1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MDH2@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MDP1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME1@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">METTL26@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MFAP4@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MFAP4@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MFN2@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MGLL@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MLEC@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MPDU1@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MPI@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MPO@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRPL47@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRPS18B@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRPS27@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRPS36@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MT-ND1@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MT-ND3@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MTCH2@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MTHFD1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MTRES1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYH14@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYLK2@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYO18A@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYPN@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NARS1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAXE@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDRG2@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDRG2@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDRG2@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDUFA11@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDUFA12@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDUFA3@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDUFA3@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDUFAB1@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDUFAF3@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDUFAF4@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDUFB11@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDUFB11@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDUFB7@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDUFB9@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDUFB9@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDUFS4@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDUFS7@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEK7@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NHLRC2@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIBAN1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NPLOC4@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NT5C@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NUBP1@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NUBP2@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NUDT16@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OGDH@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OTUB1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OXCT1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P4HB@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PABPC4@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PACSIN3@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PADI2@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAFAH1B3@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAIP1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PALMD@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PARVA@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PBXIP1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCBD1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDCD5@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDCD5@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDLIM3@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDPR@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PFKFB1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PGAM2@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PGM5@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PGP@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHB@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHB2@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIN1@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PKM@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLGRKT@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PM20D2@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POLDIP2@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPIC@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPIF@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPM1A@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPM1B@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPM1B@T3</t>
+  </si>
+  <si>
     <t xml:space="preserve">PPP1R2@T3</t>
   </si>
   <si>
+    <t xml:space="preserve">PPP1R3A@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPP3CA@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPP3CB@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPP3R1@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PREP@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRKACA@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRKCSH@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRKRA@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRXL2A@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSAP@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSAPL1@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMA7@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMB1@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMB1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMB2@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMB2@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMB3@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMB5@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMC4@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMD12@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMD2@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMD7@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMD8@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSME3@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMF1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PTPN11@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAB1A@T2</t>
+  </si>
+  <si>
     <t xml:space="preserve">RAD23B@T3</t>
   </si>
   <si>
+    <t xml:space="preserve">RANBP1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBBP4@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RDX@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REEP5@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REEP5@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROMO1@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPA2@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPA2@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL12@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL13A@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL15@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL17@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL6@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL7A@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPS20@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPS20@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RRAS2@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RTN3@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RTN3@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RTN4IP1@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RTRAF@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUVBL1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUVBL2@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUVBL2@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S100A1@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S100A1@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S100A1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S100A13@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAMM50@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCCPDH@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCCPDH@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCP2@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SDHA@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SDHB@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SDHD@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEC23A@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEC24C@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SELENBP1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEPTIN6@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SETD7@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SFXN1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SGTA@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLC16A1@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLC16A1@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLC16A1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLC25A11@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLC25A11@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLC25A13@T1</t>
+  </si>
+  <si>
     <t xml:space="preserve">SLC25A3@T3</t>
   </si>
   <si>
+    <t xml:space="preserve">SLC25A4@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLC25A6@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLC37A4@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLIRP@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMIM4@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMTN@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNTA1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNX5@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOD2@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPPL2A@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPTAN1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRSF2@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STIP1@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STK38L@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STOML2@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STT3B@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STUB1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUB1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUCLA2@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUCLG1@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SYNC@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SYNC@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TARDBP@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCAP@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TGM2@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TGM2@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIMM21@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIMM9@T1</t>
+  </si>
+  <si>
     <t xml:space="preserve">TMEM11@T1</t>
   </si>
   <si>
-    <t xml:space="preserve">ACAA1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACAT1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACSF2@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACSF2@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACSL1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACSS2@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACTR1A@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AHCYL2@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AIFM1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AIMP1@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AIMP2@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AK1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AK2@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AKT2@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALDH1A1@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALDH1L1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALPK3@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMPD1@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMPD1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMPD3@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANK1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANXA2@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANXA5@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANXA5@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANXA7@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APEH@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AQP1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARHGAP19@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARL6IP5@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARMT1@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARMT1@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARPP19@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATAD3A@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP2A3@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP5PD@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP6V1H@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BCL2L13@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BDH1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BDH2@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BLVRA@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BLVRA@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BOLA2@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSG@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BZW1@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C11orf54@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C11orf68@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA3@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAMK2A@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAMK2D@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAMK2G@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CANX@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAPN2@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CASQ1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAV2@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAVIN4@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD59@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHCHD2@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHCHD7@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHMP2A@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIRBP@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIRBP@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CKM@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLIP1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLPP@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CMPK1@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CNDP2@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CNIH4@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COL18A1@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COL4A2@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COQ3@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COQ8A@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COX19@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COX5A@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COX6B1@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CPNE1@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CPT1A@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CPT1A@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CPT1B@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CPT2@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CRIP2@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTBP1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CUL1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CUL2@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CYB5R1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CYCS@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCUN1D1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DDX1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DHRS7@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DLAT@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DLST@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DLST@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMD@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DNAJA3@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DNAJA3@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DUSP3@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DYNC1H1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DYNC1I2@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DYNLT1@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ECHDC2@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ECHDC2@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ECPAS@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EEF1A1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EEF1D@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF2A@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF2S3@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF3B@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF3C@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF3C@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF3F@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF3G@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF3G@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF3G@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF4H@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ELOB@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ELOC@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENDOD1@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENO2@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENO3@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EPB41@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ERO1A@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESYT2@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EZR@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FAH@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FAM114A2@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FARSB@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FARSB@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FHL1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FITM1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FITM2@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FKBP4@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FLOT2@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FTH1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GAA@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GANAB@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GAPDHS@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GARNL3@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLOD4@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLRX3@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLRX5@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLUL@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GMPPB@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GPX1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GPX4@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GSTP1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GYPC@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HADHA@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HARS1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HBS1L@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HDHD2@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HECTD1@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HINT1@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HINT3@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HMGCL@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HMGCL@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HNRNPDL@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HNRNPK@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPCAL1@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSPB2@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSPB3@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSPB3@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFITM1@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IPO7@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ISYNA1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JPT2@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KCTD12@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIF5B@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAMTOR1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAMTOR3@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LANCL1@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LANCL2@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAP3@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LETM1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LMAN2@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LMOD3@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LONP1@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LPCAT3@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LPCAT3@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LYPLA2@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LYRM7@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LZIC@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAN2C1@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAP1LC3B2@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAP1LC3B2@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAP2K1@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAP2K1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAP2K2@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAP2K2@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAP3K20@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAPRE2@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAPRE3@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MBNL1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MDH2@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MDP1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME1@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">METTL26@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MFAP4@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MFAP4@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MFN2@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MLEC@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MPDU1@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MPI@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRPL1@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRPL47@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRPS18B@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MT-ND3@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MTCH2@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MTRES1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MYH14@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MYLK2@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MYO18A@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NARS1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDRG2@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDRG2@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDRG2@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDUFA12@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDUFA3@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDUFA3@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDUFAB1@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDUFAF3@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDUFB11@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDUFB9@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDUFS4@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDUFS7@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NIBAN1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NNMT@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NPLOC4@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NT5C@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NUBP1@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NUBP2@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NUDT16@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OTUB1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OXCT1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P4HB@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PABPC4@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PACSIN3@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAFAH1B3@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAIP1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PALMD@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PARVA@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PBXIP1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PCBD1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDCD5@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDLIM3@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDPR@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PFKFB1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PGAM2@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PGM5@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PGP@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PHB@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PHB2@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PIN1@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POLDIP2@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPIF@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPM1A@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPM1B@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPP1R3A@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPP3CA@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPP3CB@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPP3R1@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PREP@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRKACA@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRKCSH@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRKRA@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRXL2A@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSAP@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMA7@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMB1@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMB2@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMB5@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMC4@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMD12@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMD2@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMD7@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSME3@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PTPN11@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAB1A@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RANBP1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RBBP4@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RDX@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REEP5@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROMO1@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPA2@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL12@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL15@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL17@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL6@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPS20@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPS20@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RRAS2@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RTN3@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RTN3@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RTRAF@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUVBL1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUVBL2@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUVBL2@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S100A1@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S100A1@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S100A1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S100A13@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCCPDH@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCCPDH@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SDHA@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SDHB@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SDHD@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEC23A@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEC24C@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SELENBP1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SFXN1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLC16A1@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLC25A11@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLC25A11@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLC25A13@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLC25A6@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLC37A4@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMIM4@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNTA1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNX5@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOD2@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPPL2A@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRSF2@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STIP1@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STOML2@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STT3B@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STUB1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUB1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUCLG1@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SYNC@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SYNC@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCAP@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TGM2@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TGM2@T3</t>
-  </si>
-  <si>
     <t xml:space="preserve">TMEM11@T3</t>
   </si>
   <si>
+    <t xml:space="preserve">TMEM143@T1</t>
+  </si>
+  <si>
     <t xml:space="preserve">TMEM167A@T3</t>
   </si>
   <si>
     <t xml:space="preserve">TMEM43@T3</t>
   </si>
   <si>
+    <t xml:space="preserve">TMLHE@T2</t>
+  </si>
+  <si>
     <t xml:space="preserve">TMOD4@T3</t>
   </si>
   <si>
@@ -1199,7 +1523,7 @@
     <t xml:space="preserve">TPPP3@T3</t>
   </si>
   <si>
-    <t xml:space="preserve">TPRKB@T2</t>
+    <t xml:space="preserve">TSFM@T2</t>
   </si>
   <si>
     <t xml:space="preserve">TUBA3C@T3</t>
@@ -1226,6 +1550,9 @@
     <t xml:space="preserve">UCHL1@T3</t>
   </si>
   <si>
+    <t xml:space="preserve">UCHL5@T3</t>
+  </si>
+  <si>
     <t xml:space="preserve">UQCR10@T1</t>
   </si>
   <si>
@@ -1235,6 +1562,9 @@
     <t xml:space="preserve">USP15@T3</t>
   </si>
   <si>
+    <t xml:space="preserve">VAPA@T1</t>
+  </si>
+  <si>
     <t xml:space="preserve">VARS1@T3</t>
   </si>
   <si>
@@ -1247,6 +1577,9 @@
     <t xml:space="preserve">VDAC3@T1</t>
   </si>
   <si>
+    <t xml:space="preserve">VPS35@T2</t>
+  </si>
+  <si>
     <t xml:space="preserve">VPS35@T3</t>
   </si>
   <si>
@@ -1260,6 +1593,9 @@
   </si>
   <si>
     <t xml:space="preserve">YBX3@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZBTB9@T3</t>
   </si>
   <si>
     <t xml:space="preserve">ZYX@T1</t>
@@ -1649,7 +1985,7 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>5711</v>
+        <v>5696</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -1684,10 +2020,10 @@
         <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>5711</v>
+        <v>5696</v>
       </c>
       <c r="G3" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0.125</v>
@@ -1698,15 +2034,9 @@
       <c r="J3" t="n">
         <v>0.369995498067507</v>
       </c>
-      <c r="K3" t="n">
-        <v>0.417910447761194</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.160833333333333</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.236062035084323</v>
-      </c>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1727,1606 +2057,6 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" t="n">
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0.854166666666667</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="n">
-        <v>0.145833333333333</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="n">
-        <v>0.0833333333333333</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.291666666666667</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0.208333333333333</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0.104166666666667</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0.458333333333333</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0.104166666666667</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B26" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" t="n">
-        <v>0.229166666666667</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>15</v>
-      </c>
-      <c r="B30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>15</v>
-      </c>
-      <c r="B32" t="n">
-        <v>0.104166666666667</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>15</v>
-      </c>
-      <c r="B34" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>15</v>
-      </c>
-      <c r="B35" t="n">
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>15</v>
-      </c>
-      <c r="B36" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>15</v>
-      </c>
-      <c r="B37" t="n">
-        <v>0.0833333333333333</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>15</v>
-      </c>
-      <c r="B38" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>15</v>
-      </c>
-      <c r="B39" t="n">
-        <v>0.6875</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>15</v>
-      </c>
-      <c r="B40" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>15</v>
-      </c>
-      <c r="B41" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s">
-        <v>15</v>
-      </c>
-      <c r="B42" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s">
-        <v>15</v>
-      </c>
-      <c r="B43" t="n">
-        <v>0.0833333333333333</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s">
-        <v>15</v>
-      </c>
-      <c r="B44" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s">
-        <v>15</v>
-      </c>
-      <c r="B45" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46" t="n">
-        <v>0.708333333333333</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s">
-        <v>15</v>
-      </c>
-      <c r="B47" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s">
-        <v>15</v>
-      </c>
-      <c r="B48" t="n">
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s">
-        <v>15</v>
-      </c>
-      <c r="B49" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s">
-        <v>15</v>
-      </c>
-      <c r="B50" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s">
-        <v>15</v>
-      </c>
-      <c r="B51" t="n">
-        <v>0.354166666666667</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s">
-        <v>15</v>
-      </c>
-      <c r="B52" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s">
-        <v>15</v>
-      </c>
-      <c r="B53" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s">
-        <v>15</v>
-      </c>
-      <c r="B54" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s">
-        <v>15</v>
-      </c>
-      <c r="B55" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s">
-        <v>15</v>
-      </c>
-      <c r="B56" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s">
-        <v>15</v>
-      </c>
-      <c r="B57" t="n">
-        <v>0.604166666666667</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s">
-        <v>15</v>
-      </c>
-      <c r="B58" t="n">
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s">
-        <v>15</v>
-      </c>
-      <c r="B59" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s">
-        <v>15</v>
-      </c>
-      <c r="B60" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s">
-        <v>15</v>
-      </c>
-      <c r="B61" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s">
-        <v>15</v>
-      </c>
-      <c r="B62" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s">
-        <v>15</v>
-      </c>
-      <c r="B63" t="n">
-        <v>0.104166666666667</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s">
-        <v>15</v>
-      </c>
-      <c r="B64" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s">
-        <v>15</v>
-      </c>
-      <c r="B65" t="n">
-        <v>0.416666666666667</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s">
-        <v>15</v>
-      </c>
-      <c r="B66" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s">
-        <v>15</v>
-      </c>
-      <c r="B67" t="n">
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s">
-        <v>15</v>
-      </c>
-      <c r="B68" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
-        <v>15</v>
-      </c>
-      <c r="B69" t="n">
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>15</v>
-      </c>
-      <c r="B70" t="n">
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s">
-        <v>15</v>
-      </c>
-      <c r="B71" t="n">
-        <v>0.333333333333333</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s">
-        <v>15</v>
-      </c>
-      <c r="B72" t="n">
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s">
-        <v>15</v>
-      </c>
-      <c r="B73" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s">
-        <v>15</v>
-      </c>
-      <c r="B74" t="n">
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s">
-        <v>15</v>
-      </c>
-      <c r="B75" t="n">
-        <v>0.604166666666667</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s">
-        <v>15</v>
-      </c>
-      <c r="B76" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s">
-        <v>15</v>
-      </c>
-      <c r="B77" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s">
-        <v>15</v>
-      </c>
-      <c r="B78" t="n">
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s">
-        <v>15</v>
-      </c>
-      <c r="B79" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s">
-        <v>15</v>
-      </c>
-      <c r="B80" t="n">
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s">
-        <v>15</v>
-      </c>
-      <c r="B81" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s">
-        <v>15</v>
-      </c>
-      <c r="B82" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s">
-        <v>15</v>
-      </c>
-      <c r="B83" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s">
-        <v>15</v>
-      </c>
-      <c r="B84" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s">
-        <v>15</v>
-      </c>
-      <c r="B85" t="n">
-        <v>0.416666666666667</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s">
-        <v>15</v>
-      </c>
-      <c r="B86" t="n">
-        <v>0.729166666666667</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s">
-        <v>15</v>
-      </c>
-      <c r="B87" t="n">
-        <v>0.166666666666667</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s">
-        <v>15</v>
-      </c>
-      <c r="B88" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s">
-        <v>15</v>
-      </c>
-      <c r="B89" t="n">
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s">
-        <v>15</v>
-      </c>
-      <c r="B90" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s">
-        <v>15</v>
-      </c>
-      <c r="B91" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s">
-        <v>15</v>
-      </c>
-      <c r="B92" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="s">
-        <v>15</v>
-      </c>
-      <c r="B93" t="n">
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s">
-        <v>15</v>
-      </c>
-      <c r="B94" t="n">
-        <v>0.625</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s">
-        <v>15</v>
-      </c>
-      <c r="B95" t="n">
-        <v>0.104166666666667</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="s">
-        <v>15</v>
-      </c>
-      <c r="B96" t="n">
-        <v>0.666666666666667</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="s">
-        <v>15</v>
-      </c>
-      <c r="B97" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s">
-        <v>15</v>
-      </c>
-      <c r="B98" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="s">
-        <v>15</v>
-      </c>
-      <c r="B99" t="n">
-        <v>0.625</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="s">
-        <v>15</v>
-      </c>
-      <c r="B100" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s">
-        <v>15</v>
-      </c>
-      <c r="B101" t="n">
-        <v>0.666666666666667</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s">
-        <v>15</v>
-      </c>
-      <c r="B102" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s">
-        <v>15</v>
-      </c>
-      <c r="B103" t="n">
-        <v>0.1875</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="s">
-        <v>15</v>
-      </c>
-      <c r="B104" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="s">
-        <v>15</v>
-      </c>
-      <c r="B105" t="n">
-        <v>0.541666666666667</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="s">
-        <v>15</v>
-      </c>
-      <c r="B106" t="n">
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="s">
-        <v>15</v>
-      </c>
-      <c r="B107" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="s">
-        <v>15</v>
-      </c>
-      <c r="B108" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s">
-        <v>15</v>
-      </c>
-      <c r="B109" t="n">
-        <v>0.3125</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="s">
-        <v>15</v>
-      </c>
-      <c r="B110" t="n">
-        <v>0.583333333333333</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="s">
-        <v>15</v>
-      </c>
-      <c r="B111" t="n">
-        <v>0.166666666666667</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="s">
-        <v>15</v>
-      </c>
-      <c r="B112" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="s">
-        <v>15</v>
-      </c>
-      <c r="B113" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="s">
-        <v>15</v>
-      </c>
-      <c r="B114" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="s">
-        <v>15</v>
-      </c>
-      <c r="B115" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="s">
-        <v>15</v>
-      </c>
-      <c r="B116" t="n">
-        <v>0.541666666666667</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="s">
-        <v>15</v>
-      </c>
-      <c r="B117" t="n">
-        <v>0.322916666666667</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="s">
-        <v>15</v>
-      </c>
-      <c r="B118" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="s">
-        <v>15</v>
-      </c>
-      <c r="B119" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="s">
-        <v>15</v>
-      </c>
-      <c r="B120" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="s">
-        <v>15</v>
-      </c>
-      <c r="B121" t="n">
-        <v>0.208333333333333</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="s">
-        <v>15</v>
-      </c>
-      <c r="B122" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="s">
-        <v>15</v>
-      </c>
-      <c r="B123" t="n">
-        <v>0.6875</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="s">
-        <v>15</v>
-      </c>
-      <c r="B124" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="s">
-        <v>15</v>
-      </c>
-      <c r="B125" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="s">
-        <v>15</v>
-      </c>
-      <c r="B126" t="n">
-        <v>0.104166666666667</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="s">
-        <v>15</v>
-      </c>
-      <c r="B127" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="s">
-        <v>15</v>
-      </c>
-      <c r="B128" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="s">
-        <v>15</v>
-      </c>
-      <c r="B129" t="n">
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="s">
-        <v>15</v>
-      </c>
-      <c r="B130" t="n">
-        <v>0.395833333333333</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="s">
-        <v>15</v>
-      </c>
-      <c r="B131" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="s">
-        <v>15</v>
-      </c>
-      <c r="B132" t="n">
-        <v>0.791666666666667</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="s">
-        <v>15</v>
-      </c>
-      <c r="B133" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="s">
-        <v>15</v>
-      </c>
-      <c r="B134" t="n">
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="s">
-        <v>15</v>
-      </c>
-      <c r="B135" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="s">
-        <v>15</v>
-      </c>
-      <c r="B136" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="s">
-        <v>15</v>
-      </c>
-      <c r="B137" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="s">
-        <v>15</v>
-      </c>
-      <c r="B138" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="s">
-        <v>15</v>
-      </c>
-      <c r="B139" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="s">
-        <v>15</v>
-      </c>
-      <c r="B140" t="n">
-        <v>0.8125</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="s">
-        <v>15</v>
-      </c>
-      <c r="B141" t="n">
-        <v>0.270833333333333</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="s">
-        <v>15</v>
-      </c>
-      <c r="B142" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="s">
-        <v>15</v>
-      </c>
-      <c r="B143" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="s">
-        <v>15</v>
-      </c>
-      <c r="B144" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="s">
-        <v>15</v>
-      </c>
-      <c r="B145" t="n">
-        <v>0.520833333333333</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="s">
-        <v>15</v>
-      </c>
-      <c r="B146" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="s">
-        <v>15</v>
-      </c>
-      <c r="B147" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="s">
-        <v>15</v>
-      </c>
-      <c r="B148" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="s">
-        <v>15</v>
-      </c>
-      <c r="B149" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="s">
-        <v>15</v>
-      </c>
-      <c r="B150" t="n">
-        <v>0.770833333333333</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="s">
-        <v>15</v>
-      </c>
-      <c r="B151" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="s">
-        <v>15</v>
-      </c>
-      <c r="B152" t="n">
-        <v>0.104166666666667</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="s">
-        <v>15</v>
-      </c>
-      <c r="B153" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="s">
-        <v>15</v>
-      </c>
-      <c r="B154" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="s">
-        <v>15</v>
-      </c>
-      <c r="B155" t="n">
-        <v>0.354166666666667</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="s">
-        <v>15</v>
-      </c>
-      <c r="B156" t="n">
-        <v>0.541666666666667</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="s">
-        <v>15</v>
-      </c>
-      <c r="B157" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="s">
-        <v>15</v>
-      </c>
-      <c r="B158" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="s">
-        <v>15</v>
-      </c>
-      <c r="B159" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s">
-        <v>15</v>
-      </c>
-      <c r="B160" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="s">
-        <v>15</v>
-      </c>
-      <c r="B161" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="s">
-        <v>15</v>
-      </c>
-      <c r="B162" t="n">
-        <v>0.541666666666667</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="s">
-        <v>15</v>
-      </c>
-      <c r="B163" t="n">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="s">
-        <v>15</v>
-      </c>
-      <c r="B164" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="s">
-        <v>15</v>
-      </c>
-      <c r="B165" t="n">
-        <v>0.6875</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="s">
-        <v>15</v>
-      </c>
-      <c r="B166" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="s">
-        <v>15</v>
-      </c>
-      <c r="B167" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="s">
-        <v>15</v>
-      </c>
-      <c r="B168" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="s">
-        <v>15</v>
-      </c>
-      <c r="B169" t="n">
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="s">
-        <v>15</v>
-      </c>
-      <c r="B170" t="n">
-        <v>0.145833333333333</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="s">
-        <v>15</v>
-      </c>
-      <c r="B171" t="n">
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="s">
-        <v>15</v>
-      </c>
-      <c r="B172" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="s">
-        <v>15</v>
-      </c>
-      <c r="B173" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="s">
-        <v>15</v>
-      </c>
-      <c r="B174" t="n">
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="s">
-        <v>15</v>
-      </c>
-      <c r="B175" t="n">
-        <v>0.104166666666667</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="s">
-        <v>15</v>
-      </c>
-      <c r="B176" t="n">
-        <v>0.447916666666667</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="s">
-        <v>15</v>
-      </c>
-      <c r="B177" t="n">
-        <v>0.354166666666667</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="s">
-        <v>15</v>
-      </c>
-      <c r="B178" t="n">
-        <v>0.1875</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="s">
-        <v>15</v>
-      </c>
-      <c r="B179" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="s">
-        <v>15</v>
-      </c>
-      <c r="B180" t="n">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="s">
-        <v>15</v>
-      </c>
-      <c r="B181" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="s">
-        <v>15</v>
-      </c>
-      <c r="B182" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="s">
-        <v>15</v>
-      </c>
-      <c r="B183" t="n">
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="s">
-        <v>15</v>
-      </c>
-      <c r="B184" t="n">
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="s">
-        <v>15</v>
-      </c>
-      <c r="B185" t="n">
-        <v>0.979166666666667</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="s">
-        <v>15</v>
-      </c>
-      <c r="B186" t="n">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="s">
-        <v>15</v>
-      </c>
-      <c r="B187" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="s">
-        <v>15</v>
-      </c>
-      <c r="B188" t="n">
-        <v>0.333333333333333</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="s">
-        <v>15</v>
-      </c>
-      <c r="B189" t="n">
-        <v>0.979166666666667</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="s">
-        <v>15</v>
-      </c>
-      <c r="B190" t="n">
-        <v>0.0625</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="s">
-        <v>15</v>
-      </c>
-      <c r="B191" t="n">
-        <v>0.583333333333333</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="s">
-        <v>15</v>
-      </c>
-      <c r="B192" t="n">
-        <v>0.229166666666667</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="s">
-        <v>15</v>
-      </c>
-      <c r="B193" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="s">
-        <v>15</v>
-      </c>
-      <c r="B194" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="s">
-        <v>15</v>
-      </c>
-      <c r="B195" t="n">
-        <v>0.0833333333333333</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="s">
-        <v>15</v>
-      </c>
-      <c r="B196" t="n">
-        <v>0.104166666666667</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="s">
-        <v>15</v>
-      </c>
-      <c r="B197" t="n">
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="s">
-        <v>15</v>
-      </c>
-      <c r="B198" t="n">
-        <v>0.4375</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="s">
-        <v>15</v>
-      </c>
-      <c r="B199" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="s">
-        <v>15</v>
-      </c>
-      <c r="B200" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="s">
-        <v>15</v>
-      </c>
-      <c r="B201" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -3447,7 +2177,7 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.49721345924229</v>
+        <v>0.461538461538462</v>
       </c>
     </row>
     <row r="9">
@@ -3517,7 +2247,7 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0231023884441738</v>
+        <v>0.0183300362649068</v>
       </c>
     </row>
     <row r="14">
@@ -3581,10 +2311,10 @@
         <v>38</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="3">
@@ -3595,10 +2325,10 @@
         <v>39</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="4">
@@ -3609,10 +2339,10 @@
         <v>40</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="5">
@@ -3623,10 +2353,10 @@
         <v>41</v>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="6">
@@ -3637,10 +2367,10 @@
         <v>42</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="7">
@@ -3651,10 +2381,10 @@
         <v>43</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="8">
@@ -3665,10 +2395,10 @@
         <v>44</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="9">
@@ -3679,10 +2409,10 @@
         <v>45</v>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="10">
@@ -8862,6 +7592,1574 @@
         <v>1</v>
       </c>
       <c r="D379" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="s">
+        <v>15</v>
+      </c>
+      <c r="B380" t="s">
+        <v>416</v>
+      </c>
+      <c r="C380" t="n">
+        <v>1</v>
+      </c>
+      <c r="D380" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="s">
+        <v>15</v>
+      </c>
+      <c r="B381" t="s">
+        <v>417</v>
+      </c>
+      <c r="C381" t="n">
+        <v>1</v>
+      </c>
+      <c r="D381" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="s">
+        <v>15</v>
+      </c>
+      <c r="B382" t="s">
+        <v>418</v>
+      </c>
+      <c r="C382" t="n">
+        <v>1</v>
+      </c>
+      <c r="D382" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="s">
+        <v>15</v>
+      </c>
+      <c r="B383" t="s">
+        <v>419</v>
+      </c>
+      <c r="C383" t="n">
+        <v>1</v>
+      </c>
+      <c r="D383" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="s">
+        <v>15</v>
+      </c>
+      <c r="B384" t="s">
+        <v>420</v>
+      </c>
+      <c r="C384" t="n">
+        <v>1</v>
+      </c>
+      <c r="D384" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="s">
+        <v>15</v>
+      </c>
+      <c r="B385" t="s">
+        <v>421</v>
+      </c>
+      <c r="C385" t="n">
+        <v>1</v>
+      </c>
+      <c r="D385" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="s">
+        <v>15</v>
+      </c>
+      <c r="B386" t="s">
+        <v>422</v>
+      </c>
+      <c r="C386" t="n">
+        <v>1</v>
+      </c>
+      <c r="D386" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="s">
+        <v>15</v>
+      </c>
+      <c r="B387" t="s">
+        <v>423</v>
+      </c>
+      <c r="C387" t="n">
+        <v>1</v>
+      </c>
+      <c r="D387" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="s">
+        <v>15</v>
+      </c>
+      <c r="B388" t="s">
+        <v>424</v>
+      </c>
+      <c r="C388" t="n">
+        <v>1</v>
+      </c>
+      <c r="D388" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="s">
+        <v>15</v>
+      </c>
+      <c r="B389" t="s">
+        <v>425</v>
+      </c>
+      <c r="C389" t="n">
+        <v>1</v>
+      </c>
+      <c r="D389" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="s">
+        <v>15</v>
+      </c>
+      <c r="B390" t="s">
+        <v>426</v>
+      </c>
+      <c r="C390" t="n">
+        <v>1</v>
+      </c>
+      <c r="D390" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="s">
+        <v>15</v>
+      </c>
+      <c r="B391" t="s">
+        <v>427</v>
+      </c>
+      <c r="C391" t="n">
+        <v>1</v>
+      </c>
+      <c r="D391" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="s">
+        <v>15</v>
+      </c>
+      <c r="B392" t="s">
+        <v>428</v>
+      </c>
+      <c r="C392" t="n">
+        <v>1</v>
+      </c>
+      <c r="D392" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="s">
+        <v>15</v>
+      </c>
+      <c r="B393" t="s">
+        <v>429</v>
+      </c>
+      <c r="C393" t="n">
+        <v>1</v>
+      </c>
+      <c r="D393" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="s">
+        <v>15</v>
+      </c>
+      <c r="B394" t="s">
+        <v>430</v>
+      </c>
+      <c r="C394" t="n">
+        <v>1</v>
+      </c>
+      <c r="D394" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="s">
+        <v>15</v>
+      </c>
+      <c r="B395" t="s">
+        <v>431</v>
+      </c>
+      <c r="C395" t="n">
+        <v>1</v>
+      </c>
+      <c r="D395" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="s">
+        <v>15</v>
+      </c>
+      <c r="B396" t="s">
+        <v>432</v>
+      </c>
+      <c r="C396" t="n">
+        <v>1</v>
+      </c>
+      <c r="D396" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="s">
+        <v>15</v>
+      </c>
+      <c r="B397" t="s">
+        <v>433</v>
+      </c>
+      <c r="C397" t="n">
+        <v>1</v>
+      </c>
+      <c r="D397" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="s">
+        <v>15</v>
+      </c>
+      <c r="B398" t="s">
+        <v>434</v>
+      </c>
+      <c r="C398" t="n">
+        <v>1</v>
+      </c>
+      <c r="D398" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="s">
+        <v>15</v>
+      </c>
+      <c r="B399" t="s">
+        <v>435</v>
+      </c>
+      <c r="C399" t="n">
+        <v>1</v>
+      </c>
+      <c r="D399" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="s">
+        <v>15</v>
+      </c>
+      <c r="B400" t="s">
+        <v>436</v>
+      </c>
+      <c r="C400" t="n">
+        <v>1</v>
+      </c>
+      <c r="D400" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="s">
+        <v>15</v>
+      </c>
+      <c r="B401" t="s">
+        <v>437</v>
+      </c>
+      <c r="C401" t="n">
+        <v>1</v>
+      </c>
+      <c r="D401" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="s">
+        <v>15</v>
+      </c>
+      <c r="B402" t="s">
+        <v>438</v>
+      </c>
+      <c r="C402" t="n">
+        <v>1</v>
+      </c>
+      <c r="D402" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="s">
+        <v>15</v>
+      </c>
+      <c r="B403" t="s">
+        <v>439</v>
+      </c>
+      <c r="C403" t="n">
+        <v>1</v>
+      </c>
+      <c r="D403" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="s">
+        <v>15</v>
+      </c>
+      <c r="B404" t="s">
+        <v>440</v>
+      </c>
+      <c r="C404" t="n">
+        <v>1</v>
+      </c>
+      <c r="D404" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="s">
+        <v>15</v>
+      </c>
+      <c r="B405" t="s">
+        <v>441</v>
+      </c>
+      <c r="C405" t="n">
+        <v>1</v>
+      </c>
+      <c r="D405" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="s">
+        <v>15</v>
+      </c>
+      <c r="B406" t="s">
+        <v>442</v>
+      </c>
+      <c r="C406" t="n">
+        <v>1</v>
+      </c>
+      <c r="D406" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="s">
+        <v>15</v>
+      </c>
+      <c r="B407" t="s">
+        <v>443</v>
+      </c>
+      <c r="C407" t="n">
+        <v>1</v>
+      </c>
+      <c r="D407" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="s">
+        <v>15</v>
+      </c>
+      <c r="B408" t="s">
+        <v>444</v>
+      </c>
+      <c r="C408" t="n">
+        <v>1</v>
+      </c>
+      <c r="D408" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="s">
+        <v>15</v>
+      </c>
+      <c r="B409" t="s">
+        <v>445</v>
+      </c>
+      <c r="C409" t="n">
+        <v>1</v>
+      </c>
+      <c r="D409" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="s">
+        <v>15</v>
+      </c>
+      <c r="B410" t="s">
+        <v>446</v>
+      </c>
+      <c r="C410" t="n">
+        <v>1</v>
+      </c>
+      <c r="D410" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="s">
+        <v>15</v>
+      </c>
+      <c r="B411" t="s">
+        <v>447</v>
+      </c>
+      <c r="C411" t="n">
+        <v>1</v>
+      </c>
+      <c r="D411" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="s">
+        <v>15</v>
+      </c>
+      <c r="B412" t="s">
+        <v>448</v>
+      </c>
+      <c r="C412" t="n">
+        <v>1</v>
+      </c>
+      <c r="D412" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="s">
+        <v>15</v>
+      </c>
+      <c r="B413" t="s">
+        <v>449</v>
+      </c>
+      <c r="C413" t="n">
+        <v>1</v>
+      </c>
+      <c r="D413" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="s">
+        <v>15</v>
+      </c>
+      <c r="B414" t="s">
+        <v>450</v>
+      </c>
+      <c r="C414" t="n">
+        <v>1</v>
+      </c>
+      <c r="D414" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="s">
+        <v>15</v>
+      </c>
+      <c r="B415" t="s">
+        <v>451</v>
+      </c>
+      <c r="C415" t="n">
+        <v>1</v>
+      </c>
+      <c r="D415" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="s">
+        <v>15</v>
+      </c>
+      <c r="B416" t="s">
+        <v>452</v>
+      </c>
+      <c r="C416" t="n">
+        <v>1</v>
+      </c>
+      <c r="D416" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="s">
+        <v>15</v>
+      </c>
+      <c r="B417" t="s">
+        <v>453</v>
+      </c>
+      <c r="C417" t="n">
+        <v>1</v>
+      </c>
+      <c r="D417" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="s">
+        <v>15</v>
+      </c>
+      <c r="B418" t="s">
+        <v>454</v>
+      </c>
+      <c r="C418" t="n">
+        <v>1</v>
+      </c>
+      <c r="D418" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="s">
+        <v>15</v>
+      </c>
+      <c r="B419" t="s">
+        <v>455</v>
+      </c>
+      <c r="C419" t="n">
+        <v>1</v>
+      </c>
+      <c r="D419" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="s">
+        <v>15</v>
+      </c>
+      <c r="B420" t="s">
+        <v>456</v>
+      </c>
+      <c r="C420" t="n">
+        <v>1</v>
+      </c>
+      <c r="D420" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="s">
+        <v>15</v>
+      </c>
+      <c r="B421" t="s">
+        <v>457</v>
+      </c>
+      <c r="C421" t="n">
+        <v>1</v>
+      </c>
+      <c r="D421" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="s">
+        <v>15</v>
+      </c>
+      <c r="B422" t="s">
+        <v>458</v>
+      </c>
+      <c r="C422" t="n">
+        <v>1</v>
+      </c>
+      <c r="D422" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="s">
+        <v>15</v>
+      </c>
+      <c r="B423" t="s">
+        <v>459</v>
+      </c>
+      <c r="C423" t="n">
+        <v>1</v>
+      </c>
+      <c r="D423" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="s">
+        <v>15</v>
+      </c>
+      <c r="B424" t="s">
+        <v>460</v>
+      </c>
+      <c r="C424" t="n">
+        <v>1</v>
+      </c>
+      <c r="D424" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="s">
+        <v>15</v>
+      </c>
+      <c r="B425" t="s">
+        <v>461</v>
+      </c>
+      <c r="C425" t="n">
+        <v>1</v>
+      </c>
+      <c r="D425" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="s">
+        <v>15</v>
+      </c>
+      <c r="B426" t="s">
+        <v>462</v>
+      </c>
+      <c r="C426" t="n">
+        <v>1</v>
+      </c>
+      <c r="D426" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="s">
+        <v>15</v>
+      </c>
+      <c r="B427" t="s">
+        <v>463</v>
+      </c>
+      <c r="C427" t="n">
+        <v>1</v>
+      </c>
+      <c r="D427" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="s">
+        <v>15</v>
+      </c>
+      <c r="B428" t="s">
+        <v>464</v>
+      </c>
+      <c r="C428" t="n">
+        <v>1</v>
+      </c>
+      <c r="D428" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="s">
+        <v>15</v>
+      </c>
+      <c r="B429" t="s">
+        <v>465</v>
+      </c>
+      <c r="C429" t="n">
+        <v>1</v>
+      </c>
+      <c r="D429" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="s">
+        <v>15</v>
+      </c>
+      <c r="B430" t="s">
+        <v>466</v>
+      </c>
+      <c r="C430" t="n">
+        <v>1</v>
+      </c>
+      <c r="D430" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="s">
+        <v>15</v>
+      </c>
+      <c r="B431" t="s">
+        <v>467</v>
+      </c>
+      <c r="C431" t="n">
+        <v>1</v>
+      </c>
+      <c r="D431" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="s">
+        <v>15</v>
+      </c>
+      <c r="B432" t="s">
+        <v>468</v>
+      </c>
+      <c r="C432" t="n">
+        <v>1</v>
+      </c>
+      <c r="D432" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="s">
+        <v>15</v>
+      </c>
+      <c r="B433" t="s">
+        <v>469</v>
+      </c>
+      <c r="C433" t="n">
+        <v>1</v>
+      </c>
+      <c r="D433" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="s">
+        <v>15</v>
+      </c>
+      <c r="B434" t="s">
+        <v>470</v>
+      </c>
+      <c r="C434" t="n">
+        <v>1</v>
+      </c>
+      <c r="D434" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="s">
+        <v>15</v>
+      </c>
+      <c r="B435" t="s">
+        <v>471</v>
+      </c>
+      <c r="C435" t="n">
+        <v>1</v>
+      </c>
+      <c r="D435" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="s">
+        <v>15</v>
+      </c>
+      <c r="B436" t="s">
+        <v>472</v>
+      </c>
+      <c r="C436" t="n">
+        <v>1</v>
+      </c>
+      <c r="D436" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="s">
+        <v>15</v>
+      </c>
+      <c r="B437" t="s">
+        <v>473</v>
+      </c>
+      <c r="C437" t="n">
+        <v>1</v>
+      </c>
+      <c r="D437" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="s">
+        <v>15</v>
+      </c>
+      <c r="B438" t="s">
+        <v>474</v>
+      </c>
+      <c r="C438" t="n">
+        <v>1</v>
+      </c>
+      <c r="D438" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="s">
+        <v>15</v>
+      </c>
+      <c r="B439" t="s">
+        <v>475</v>
+      </c>
+      <c r="C439" t="n">
+        <v>1</v>
+      </c>
+      <c r="D439" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="s">
+        <v>15</v>
+      </c>
+      <c r="B440" t="s">
+        <v>476</v>
+      </c>
+      <c r="C440" t="n">
+        <v>1</v>
+      </c>
+      <c r="D440" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="s">
+        <v>15</v>
+      </c>
+      <c r="B441" t="s">
+        <v>477</v>
+      </c>
+      <c r="C441" t="n">
+        <v>1</v>
+      </c>
+      <c r="D441" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="s">
+        <v>15</v>
+      </c>
+      <c r="B442" t="s">
+        <v>478</v>
+      </c>
+      <c r="C442" t="n">
+        <v>1</v>
+      </c>
+      <c r="D442" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="s">
+        <v>15</v>
+      </c>
+      <c r="B443" t="s">
+        <v>479</v>
+      </c>
+      <c r="C443" t="n">
+        <v>1</v>
+      </c>
+      <c r="D443" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="s">
+        <v>15</v>
+      </c>
+      <c r="B444" t="s">
+        <v>480</v>
+      </c>
+      <c r="C444" t="n">
+        <v>1</v>
+      </c>
+      <c r="D444" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="s">
+        <v>15</v>
+      </c>
+      <c r="B445" t="s">
+        <v>481</v>
+      </c>
+      <c r="C445" t="n">
+        <v>1</v>
+      </c>
+      <c r="D445" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="s">
+        <v>15</v>
+      </c>
+      <c r="B446" t="s">
+        <v>482</v>
+      </c>
+      <c r="C446" t="n">
+        <v>1</v>
+      </c>
+      <c r="D446" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="s">
+        <v>15</v>
+      </c>
+      <c r="B447" t="s">
+        <v>483</v>
+      </c>
+      <c r="C447" t="n">
+        <v>1</v>
+      </c>
+      <c r="D447" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="s">
+        <v>15</v>
+      </c>
+      <c r="B448" t="s">
+        <v>484</v>
+      </c>
+      <c r="C448" t="n">
+        <v>1</v>
+      </c>
+      <c r="D448" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="s">
+        <v>15</v>
+      </c>
+      <c r="B449" t="s">
+        <v>485</v>
+      </c>
+      <c r="C449" t="n">
+        <v>1</v>
+      </c>
+      <c r="D449" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="s">
+        <v>15</v>
+      </c>
+      <c r="B450" t="s">
+        <v>486</v>
+      </c>
+      <c r="C450" t="n">
+        <v>1</v>
+      </c>
+      <c r="D450" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="s">
+        <v>15</v>
+      </c>
+      <c r="B451" t="s">
+        <v>487</v>
+      </c>
+      <c r="C451" t="n">
+        <v>1</v>
+      </c>
+      <c r="D451" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="s">
+        <v>15</v>
+      </c>
+      <c r="B452" t="s">
+        <v>488</v>
+      </c>
+      <c r="C452" t="n">
+        <v>1</v>
+      </c>
+      <c r="D452" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="s">
+        <v>15</v>
+      </c>
+      <c r="B453" t="s">
+        <v>489</v>
+      </c>
+      <c r="C453" t="n">
+        <v>1</v>
+      </c>
+      <c r="D453" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="s">
+        <v>15</v>
+      </c>
+      <c r="B454" t="s">
+        <v>490</v>
+      </c>
+      <c r="C454" t="n">
+        <v>1</v>
+      </c>
+      <c r="D454" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="s">
+        <v>15</v>
+      </c>
+      <c r="B455" t="s">
+        <v>491</v>
+      </c>
+      <c r="C455" t="n">
+        <v>1</v>
+      </c>
+      <c r="D455" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="s">
+        <v>15</v>
+      </c>
+      <c r="B456" t="s">
+        <v>492</v>
+      </c>
+      <c r="C456" t="n">
+        <v>1</v>
+      </c>
+      <c r="D456" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="s">
+        <v>15</v>
+      </c>
+      <c r="B457" t="s">
+        <v>493</v>
+      </c>
+      <c r="C457" t="n">
+        <v>1</v>
+      </c>
+      <c r="D457" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="s">
+        <v>15</v>
+      </c>
+      <c r="B458" t="s">
+        <v>494</v>
+      </c>
+      <c r="C458" t="n">
+        <v>1</v>
+      </c>
+      <c r="D458" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="s">
+        <v>15</v>
+      </c>
+      <c r="B459" t="s">
+        <v>495</v>
+      </c>
+      <c r="C459" t="n">
+        <v>1</v>
+      </c>
+      <c r="D459" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="s">
+        <v>15</v>
+      </c>
+      <c r="B460" t="s">
+        <v>496</v>
+      </c>
+      <c r="C460" t="n">
+        <v>1</v>
+      </c>
+      <c r="D460" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="s">
+        <v>15</v>
+      </c>
+      <c r="B461" t="s">
+        <v>497</v>
+      </c>
+      <c r="C461" t="n">
+        <v>1</v>
+      </c>
+      <c r="D461" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="s">
+        <v>15</v>
+      </c>
+      <c r="B462" t="s">
+        <v>498</v>
+      </c>
+      <c r="C462" t="n">
+        <v>1</v>
+      </c>
+      <c r="D462" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="s">
+        <v>15</v>
+      </c>
+      <c r="B463" t="s">
+        <v>499</v>
+      </c>
+      <c r="C463" t="n">
+        <v>1</v>
+      </c>
+      <c r="D463" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="s">
+        <v>15</v>
+      </c>
+      <c r="B464" t="s">
+        <v>500</v>
+      </c>
+      <c r="C464" t="n">
+        <v>1</v>
+      </c>
+      <c r="D464" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="s">
+        <v>15</v>
+      </c>
+      <c r="B465" t="s">
+        <v>501</v>
+      </c>
+      <c r="C465" t="n">
+        <v>1</v>
+      </c>
+      <c r="D465" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="s">
+        <v>15</v>
+      </c>
+      <c r="B466" t="s">
+        <v>502</v>
+      </c>
+      <c r="C466" t="n">
+        <v>1</v>
+      </c>
+      <c r="D466" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="s">
+        <v>15</v>
+      </c>
+      <c r="B467" t="s">
+        <v>503</v>
+      </c>
+      <c r="C467" t="n">
+        <v>1</v>
+      </c>
+      <c r="D467" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="s">
+        <v>15</v>
+      </c>
+      <c r="B468" t="s">
+        <v>504</v>
+      </c>
+      <c r="C468" t="n">
+        <v>1</v>
+      </c>
+      <c r="D468" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="s">
+        <v>15</v>
+      </c>
+      <c r="B469" t="s">
+        <v>505</v>
+      </c>
+      <c r="C469" t="n">
+        <v>1</v>
+      </c>
+      <c r="D469" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="s">
+        <v>15</v>
+      </c>
+      <c r="B470" t="s">
+        <v>506</v>
+      </c>
+      <c r="C470" t="n">
+        <v>1</v>
+      </c>
+      <c r="D470" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="s">
+        <v>15</v>
+      </c>
+      <c r="B471" t="s">
+        <v>507</v>
+      </c>
+      <c r="C471" t="n">
+        <v>1</v>
+      </c>
+      <c r="D471" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="s">
+        <v>15</v>
+      </c>
+      <c r="B472" t="s">
+        <v>508</v>
+      </c>
+      <c r="C472" t="n">
+        <v>1</v>
+      </c>
+      <c r="D472" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="s">
+        <v>15</v>
+      </c>
+      <c r="B473" t="s">
+        <v>509</v>
+      </c>
+      <c r="C473" t="n">
+        <v>1</v>
+      </c>
+      <c r="D473" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="s">
+        <v>15</v>
+      </c>
+      <c r="B474" t="s">
+        <v>510</v>
+      </c>
+      <c r="C474" t="n">
+        <v>1</v>
+      </c>
+      <c r="D474" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="s">
+        <v>15</v>
+      </c>
+      <c r="B475" t="s">
+        <v>511</v>
+      </c>
+      <c r="C475" t="n">
+        <v>1</v>
+      </c>
+      <c r="D475" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="s">
+        <v>15</v>
+      </c>
+      <c r="B476" t="s">
+        <v>512</v>
+      </c>
+      <c r="C476" t="n">
+        <v>1</v>
+      </c>
+      <c r="D476" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="s">
+        <v>15</v>
+      </c>
+      <c r="B477" t="s">
+        <v>513</v>
+      </c>
+      <c r="C477" t="n">
+        <v>1</v>
+      </c>
+      <c r="D477" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="s">
+        <v>15</v>
+      </c>
+      <c r="B478" t="s">
+        <v>514</v>
+      </c>
+      <c r="C478" t="n">
+        <v>1</v>
+      </c>
+      <c r="D478" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="s">
+        <v>15</v>
+      </c>
+      <c r="B479" t="s">
+        <v>515</v>
+      </c>
+      <c r="C479" t="n">
+        <v>1</v>
+      </c>
+      <c r="D479" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="s">
+        <v>15</v>
+      </c>
+      <c r="B480" t="s">
+        <v>516</v>
+      </c>
+      <c r="C480" t="n">
+        <v>1</v>
+      </c>
+      <c r="D480" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="s">
+        <v>15</v>
+      </c>
+      <c r="B481" t="s">
+        <v>517</v>
+      </c>
+      <c r="C481" t="n">
+        <v>1</v>
+      </c>
+      <c r="D481" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="s">
+        <v>15</v>
+      </c>
+      <c r="B482" t="s">
+        <v>518</v>
+      </c>
+      <c r="C482" t="n">
+        <v>1</v>
+      </c>
+      <c r="D482" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="s">
+        <v>15</v>
+      </c>
+      <c r="B483" t="s">
+        <v>519</v>
+      </c>
+      <c r="C483" t="n">
+        <v>1</v>
+      </c>
+      <c r="D483" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="s">
+        <v>15</v>
+      </c>
+      <c r="B484" t="s">
+        <v>520</v>
+      </c>
+      <c r="C484" t="n">
+        <v>1</v>
+      </c>
+      <c r="D484" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="s">
+        <v>15</v>
+      </c>
+      <c r="B485" t="s">
+        <v>521</v>
+      </c>
+      <c r="C485" t="n">
+        <v>1</v>
+      </c>
+      <c r="D485" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="s">
+        <v>15</v>
+      </c>
+      <c r="B486" t="s">
+        <v>522</v>
+      </c>
+      <c r="C486" t="n">
+        <v>1</v>
+      </c>
+      <c r="D486" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="s">
+        <v>15</v>
+      </c>
+      <c r="B487" t="s">
+        <v>523</v>
+      </c>
+      <c r="C487" t="n">
+        <v>1</v>
+      </c>
+      <c r="D487" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="s">
+        <v>15</v>
+      </c>
+      <c r="B488" t="s">
+        <v>524</v>
+      </c>
+      <c r="C488" t="n">
+        <v>1</v>
+      </c>
+      <c r="D488" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="s">
+        <v>15</v>
+      </c>
+      <c r="B489" t="s">
+        <v>525</v>
+      </c>
+      <c r="C489" t="n">
+        <v>1</v>
+      </c>
+      <c r="D489" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="s">
+        <v>15</v>
+      </c>
+      <c r="B490" t="s">
+        <v>526</v>
+      </c>
+      <c r="C490" t="n">
+        <v>1</v>
+      </c>
+      <c r="D490" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="s">
+        <v>15</v>
+      </c>
+      <c r="B491" t="s">
+        <v>527</v>
+      </c>
+      <c r="C491" t="n">
+        <v>1</v>
+      </c>
+      <c r="D491" t="n">
         <v>0.0714285714285714</v>
       </c>
     </row>

--- a/05_Figures/F05_classification/proteins/trajectory/HR_LR/pam/c_data/results.xlsx
+++ b/05_Figures/F05_classification/proteins/trajectory/HR_LR/pam/c_data/results.xlsx
@@ -2023,7 +2023,7 @@
         <v>5696</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H3" t="n">
         <v>0.125</v>
@@ -2034,9 +2034,15 @@
       <c r="J3" t="n">
         <v>0.369995498067507</v>
       </c>
-      <c r="K3"/>
-      <c r="L3"/>
-      <c r="M3"/>
+      <c r="K3" t="n">
+        <v>0.437810945273632</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.1609375</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.230934228587746</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2057,6 +2063,1606 @@
         <v>17</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.854166666666667</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.3125</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.229166666666667</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="n">
+        <v>0.333333333333333</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" t="n">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" t="n">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" t="n">
+        <v>0.270833333333333</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" t="n">
+        <v>0.104166666666667</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" t="n">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" t="n">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" t="n">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" t="n">
+        <v>0.416666666666667</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" t="n">
+        <v>0.104166666666667</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" t="n">
+        <v>0.6875</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>15</v>
+      </c>
+      <c r="B48" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51" t="n">
+        <v>0.333333333333333</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53" t="n">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>15</v>
+      </c>
+      <c r="B54" t="n">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>15</v>
+      </c>
+      <c r="B57" t="n">
+        <v>0.666666666666667</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>15</v>
+      </c>
+      <c r="B58" t="n">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>15</v>
+      </c>
+      <c r="B60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>15</v>
+      </c>
+      <c r="B62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>15</v>
+      </c>
+      <c r="B63" t="n">
+        <v>0.208333333333333</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>15</v>
+      </c>
+      <c r="B64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>15</v>
+      </c>
+      <c r="B65" t="n">
+        <v>0.395833333333333</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>15</v>
+      </c>
+      <c r="B66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>15</v>
+      </c>
+      <c r="B67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>15</v>
+      </c>
+      <c r="B68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>15</v>
+      </c>
+      <c r="B69" t="n">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>15</v>
+      </c>
+      <c r="B70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>15</v>
+      </c>
+      <c r="B71" t="n">
+        <v>0.104166666666667</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>15</v>
+      </c>
+      <c r="B72" t="n">
+        <v>0.104166666666667</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>15</v>
+      </c>
+      <c r="B73" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>15</v>
+      </c>
+      <c r="B74" t="n">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>15</v>
+      </c>
+      <c r="B75" t="n">
+        <v>0.604166666666667</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>15</v>
+      </c>
+      <c r="B76" t="n">
+        <v>0.291666666666667</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>15</v>
+      </c>
+      <c r="B77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>15</v>
+      </c>
+      <c r="B78" t="n">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>15</v>
+      </c>
+      <c r="B79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>15</v>
+      </c>
+      <c r="B80" t="n">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>15</v>
+      </c>
+      <c r="B81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>15</v>
+      </c>
+      <c r="B82" t="n">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>15</v>
+      </c>
+      <c r="B83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>15</v>
+      </c>
+      <c r="B84" t="n">
+        <v>0.104166666666667</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>15</v>
+      </c>
+      <c r="B85" t="n">
+        <v>0.229166666666667</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>15</v>
+      </c>
+      <c r="B86" t="n">
+        <v>0.833333333333333</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>15</v>
+      </c>
+      <c r="B87" t="n">
+        <v>0.166666666666667</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>15</v>
+      </c>
+      <c r="B88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>15</v>
+      </c>
+      <c r="B89" t="n">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>15</v>
+      </c>
+      <c r="B90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>15</v>
+      </c>
+      <c r="B91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>15</v>
+      </c>
+      <c r="B92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>15</v>
+      </c>
+      <c r="B93" t="n">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>15</v>
+      </c>
+      <c r="B94" t="n">
+        <v>0.6875</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>15</v>
+      </c>
+      <c r="B95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>15</v>
+      </c>
+      <c r="B96" t="n">
+        <v>0.541666666666667</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>15</v>
+      </c>
+      <c r="B97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>15</v>
+      </c>
+      <c r="B98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>15</v>
+      </c>
+      <c r="B99" t="n">
+        <v>0.645833333333333</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>15</v>
+      </c>
+      <c r="B100" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>15</v>
+      </c>
+      <c r="B101" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>15</v>
+      </c>
+      <c r="B102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>15</v>
+      </c>
+      <c r="B103" t="n">
+        <v>0.208333333333333</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>15</v>
+      </c>
+      <c r="B104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>15</v>
+      </c>
+      <c r="B105" t="n">
+        <v>0.541666666666667</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>15</v>
+      </c>
+      <c r="B106" t="n">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>15</v>
+      </c>
+      <c r="B107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>15</v>
+      </c>
+      <c r="B108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>15</v>
+      </c>
+      <c r="B109" t="n">
+        <v>0.4375</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>15</v>
+      </c>
+      <c r="B110" t="n">
+        <v>0.666666666666667</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>15</v>
+      </c>
+      <c r="B111" t="n">
+        <v>0.166666666666667</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>15</v>
+      </c>
+      <c r="B112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>15</v>
+      </c>
+      <c r="B113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>15</v>
+      </c>
+      <c r="B114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>15</v>
+      </c>
+      <c r="B115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>15</v>
+      </c>
+      <c r="B116" t="n">
+        <v>0.541666666666667</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>15</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.458333333333333</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>15</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>15</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>15</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>15</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>15</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>15</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.666666666666667</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>15</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.0625</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>15</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>15</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.208333333333333</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>15</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>15</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>15</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>15</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.395833333333333</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>15</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>15</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.791666666666667</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>15</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>15</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>15</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>15</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>15</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>15</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>15</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>15</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.729166666666667</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>15</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>15</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>15</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>15</v>
+      </c>
+      <c r="B144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>15</v>
+      </c>
+      <c r="B145" t="n">
+        <v>0.4375</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>15</v>
+      </c>
+      <c r="B146" t="n">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>15</v>
+      </c>
+      <c r="B147" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>15</v>
+      </c>
+      <c r="B148" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>15</v>
+      </c>
+      <c r="B149" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>15</v>
+      </c>
+      <c r="B150" t="n">
+        <v>0.791666666666667</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>15</v>
+      </c>
+      <c r="B151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" t="n">
+        <v>0.104166666666667</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>15</v>
+      </c>
+      <c r="B153" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>15</v>
+      </c>
+      <c r="B154" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>15</v>
+      </c>
+      <c r="B155" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>15</v>
+      </c>
+      <c r="B156" t="n">
+        <v>0.4375</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>15</v>
+      </c>
+      <c r="B157" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>15</v>
+      </c>
+      <c r="B158" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>15</v>
+      </c>
+      <c r="B159" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>15</v>
+      </c>
+      <c r="B160" t="n">
+        <v>0.3125</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>15</v>
+      </c>
+      <c r="B161" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>15</v>
+      </c>
+      <c r="B162" t="n">
+        <v>0.5625</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>15</v>
+      </c>
+      <c r="B163" t="n">
+        <v>0.416666666666667</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>15</v>
+      </c>
+      <c r="B164" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>15</v>
+      </c>
+      <c r="B165" t="n">
+        <v>0.666666666666667</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>15</v>
+      </c>
+      <c r="B166" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>15</v>
+      </c>
+      <c r="B167" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>15</v>
+      </c>
+      <c r="B168" t="n">
+        <v>0.8125</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>15</v>
+      </c>
+      <c r="B169" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>15</v>
+      </c>
+      <c r="B170" t="n">
+        <v>0.208333333333333</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>15</v>
+      </c>
+      <c r="B171" t="n">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>15</v>
+      </c>
+      <c r="B172" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>15</v>
+      </c>
+      <c r="B173" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>15</v>
+      </c>
+      <c r="B174" t="n">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>15</v>
+      </c>
+      <c r="B175" t="n">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>15</v>
+      </c>
+      <c r="B176" t="n">
+        <v>0.520833333333333</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>15</v>
+      </c>
+      <c r="B177" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>15</v>
+      </c>
+      <c r="B178" t="n">
+        <v>0.166666666666667</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>15</v>
+      </c>
+      <c r="B179" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>15</v>
+      </c>
+      <c r="B180" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>15</v>
+      </c>
+      <c r="B181" t="n">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>15</v>
+      </c>
+      <c r="B182" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>15</v>
+      </c>
+      <c r="B183" t="n">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>15</v>
+      </c>
+      <c r="B184" t="n">
+        <v>0.104166666666667</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>15</v>
+      </c>
+      <c r="B185" t="n">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>15</v>
+      </c>
+      <c r="B186" t="n">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>15</v>
+      </c>
+      <c r="B187" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>15</v>
+      </c>
+      <c r="B188" t="n">
+        <v>0.229166666666667</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>15</v>
+      </c>
+      <c r="B189" t="n">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>15</v>
+      </c>
+      <c r="B190" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>15</v>
+      </c>
+      <c r="B191" t="n">
+        <v>0.583333333333333</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>15</v>
+      </c>
+      <c r="B192" t="n">
+        <v>0.208333333333333</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>15</v>
+      </c>
+      <c r="B193" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>15</v>
+      </c>
+      <c r="B194" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>15</v>
+      </c>
+      <c r="B195" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>15</v>
+      </c>
+      <c r="B196" t="n">
+        <v>0.104166666666667</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>15</v>
+      </c>
+      <c r="B197" t="n">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>15</v>
+      </c>
+      <c r="B198" t="n">
+        <v>0.104166666666667</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>15</v>
+      </c>
+      <c r="B199" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>15</v>
+      </c>
+      <c r="B200" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>15</v>
+      </c>
+      <c r="B201" t="n">
+        <v>0.1875</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
